--- a/Outbound_Data_v2.xlsx
+++ b/Outbound_Data_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idpjsc-my.sharepoint.com/personal/lam_tranhoang_lof_vn/Documents/WAREHOUSE/CLAUDECODE/WMS webapp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="11_F0AB4012CDF32F3C18C30D855C56A941612C3F2C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A0CD60B-703E-4ED3-85EE-CFA3A7F56206}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="11_F0AB4012CDF32F3C18C30D855C56A941612C3F2C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C940DECB-B71A-4AD2-B12F-22A5994DC3D3}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Outbound" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14617" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7391" uniqueCount="732">
   <si>
     <t>Kho xuất</t>
   </si>
@@ -2599,25 +2599,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S544"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" customWidth="1"/>
-    <col min="11" max="11" width="6.83203125" customWidth="1"/>
-    <col min="12" max="14" width="8.83203125" customWidth="1"/>
-    <col min="15" max="18" width="14.83203125" customWidth="1"/>
-    <col min="19" max="19" width="10.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.875" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="20.875" customWidth="1"/>
+    <col min="4" max="4" width="12.875" customWidth="1"/>
+    <col min="5" max="5" width="16.875" customWidth="1"/>
+    <col min="6" max="6" width="10.875" customWidth="1"/>
+    <col min="7" max="7" width="22.875" customWidth="1"/>
+    <col min="8" max="8" width="12.875" customWidth="1"/>
+    <col min="9" max="9" width="14.875" customWidth="1"/>
+    <col min="10" max="10" width="8.875" customWidth="1"/>
+    <col min="11" max="11" width="6.875" customWidth="1"/>
+    <col min="12" max="14" width="8.875" customWidth="1"/>
+    <col min="15" max="18" width="14.875" customWidth="1"/>
+    <col min="19" max="19" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -3384,7 +3384,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -3561,7 +3561,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -3679,7 +3679,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -3738,7 +3738,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -3915,7 +3915,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>19</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>19</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>19</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>19</v>
       </c>
@@ -4328,7 +4328,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>19</v>
       </c>
@@ -4387,7 +4387,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>19</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>19</v>
       </c>
@@ -4505,7 +4505,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>19</v>
       </c>
@@ -4564,7 +4564,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>19</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>19</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>19</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>19</v>
       </c>
@@ -5095,7 +5095,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -5213,7 +5213,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>19</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -5331,7 +5331,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>19</v>
       </c>
@@ -5390,7 +5390,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>19</v>
       </c>
@@ -5449,7 +5449,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>19</v>
       </c>
@@ -5508,7 +5508,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>19</v>
       </c>
@@ -5567,7 +5567,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>19</v>
       </c>
@@ -5626,7 +5626,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>19</v>
       </c>
@@ -5685,7 +5685,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>19</v>
       </c>
@@ -5744,7 +5744,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>19</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>19</v>
       </c>
@@ -5862,7 +5862,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>19</v>
       </c>
@@ -5921,7 +5921,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>19</v>
       </c>
@@ -5980,7 +5980,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -6039,7 +6039,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>19</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -6157,7 +6157,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>19</v>
       </c>
@@ -6216,7 +6216,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>19</v>
       </c>
@@ -6275,7 +6275,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>19</v>
       </c>
@@ -6334,7 +6334,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>19</v>
       </c>
@@ -6393,7 +6393,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>19</v>
       </c>
@@ -6452,7 +6452,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>19</v>
       </c>
@@ -6511,7 +6511,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>19</v>
       </c>
@@ -6570,7 +6570,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>19</v>
       </c>
@@ -6629,7 +6629,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>19</v>
       </c>
@@ -6688,7 +6688,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>19</v>
       </c>
@@ -6747,7 +6747,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>19</v>
       </c>
@@ -6806,7 +6806,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>19</v>
       </c>
@@ -6865,7 +6865,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>19</v>
       </c>
@@ -6924,7 +6924,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>19</v>
       </c>
@@ -6983,7 +6983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>19</v>
       </c>
@@ -7042,7 +7042,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>19</v>
       </c>
@@ -7101,7 +7101,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>19</v>
       </c>
@@ -7160,7 +7160,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>19</v>
       </c>
@@ -7219,7 +7219,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>19</v>
       </c>
@@ -7278,7 +7278,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>19</v>
       </c>
@@ -7337,7 +7337,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>19</v>
       </c>
@@ -7396,7 +7396,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>19</v>
       </c>
@@ -7455,7 +7455,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>19</v>
       </c>
@@ -7514,7 +7514,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>19</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>19</v>
       </c>
@@ -7632,7 +7632,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>19</v>
       </c>
@@ -7691,7 +7691,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>19</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>19</v>
       </c>
@@ -7809,7 +7809,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>19</v>
       </c>
@@ -7868,7 +7868,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>19</v>
       </c>
@@ -7927,7 +7927,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>19</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>19</v>
       </c>
@@ -8045,7 +8045,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>19</v>
       </c>
@@ -8104,7 +8104,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>19</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>19</v>
       </c>
@@ -8222,7 +8222,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>19</v>
       </c>
@@ -8281,7 +8281,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>19</v>
       </c>
@@ -8340,7 +8340,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>19</v>
       </c>
@@ -8399,7 +8399,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>19</v>
       </c>
@@ -8458,7 +8458,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>19</v>
       </c>
@@ -8517,7 +8517,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>19</v>
       </c>
@@ -8576,7 +8576,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>19</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>19</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>19</v>
       </c>
@@ -8753,7 +8753,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>19</v>
       </c>
@@ -8812,7 +8812,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>19</v>
       </c>
@@ -8871,7 +8871,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>19</v>
       </c>
@@ -8930,7 +8930,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>19</v>
       </c>
@@ -8989,7 +8989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>19</v>
       </c>
@@ -9048,7 +9048,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>19</v>
       </c>
@@ -9107,7 +9107,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>19</v>
       </c>
@@ -9166,7 +9166,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>19</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>19</v>
       </c>
@@ -9284,7 +9284,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>19</v>
       </c>
@@ -9343,7 +9343,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>19</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>19</v>
       </c>
@@ -9461,7 +9461,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>19</v>
       </c>
@@ -9520,7 +9520,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>19</v>
       </c>
@@ -9579,7 +9579,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>19</v>
       </c>
@@ -9638,7 +9638,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>19</v>
       </c>
@@ -9697,7 +9697,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>19</v>
       </c>
@@ -9756,7 +9756,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>19</v>
       </c>
@@ -9815,7 +9815,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>19</v>
       </c>
@@ -9874,7 +9874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>19</v>
       </c>
@@ -9933,7 +9933,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>19</v>
       </c>
@@ -9992,7 +9992,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>19</v>
       </c>
@@ -10051,7 +10051,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>19</v>
       </c>
@@ -10110,7 +10110,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>19</v>
       </c>
@@ -10169,7 +10169,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>19</v>
       </c>
@@ -10228,7 +10228,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>19</v>
       </c>
@@ -10287,7 +10287,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>19</v>
       </c>
@@ -10346,7 +10346,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>19</v>
       </c>
@@ -10405,7 +10405,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>19</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>19</v>
       </c>
@@ -10523,7 +10523,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>19</v>
       </c>
@@ -10582,7 +10582,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>19</v>
       </c>
@@ -10641,7 +10641,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>19</v>
       </c>
@@ -10700,7 +10700,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>19</v>
       </c>
@@ -10759,7 +10759,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>19</v>
       </c>
@@ -10818,7 +10818,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>19</v>
       </c>
@@ -10877,7 +10877,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>19</v>
       </c>
@@ -10936,7 +10936,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>19</v>
       </c>
@@ -10995,7 +10995,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>19</v>
       </c>
@@ -11054,7 +11054,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>19</v>
       </c>
@@ -11113,7 +11113,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>19</v>
       </c>
@@ -11172,7 +11172,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>19</v>
       </c>
@@ -11231,7 +11231,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>19</v>
       </c>
@@ -11290,7 +11290,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>19</v>
       </c>
@@ -11349,7 +11349,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>19</v>
       </c>
@@ -11408,7 +11408,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>19</v>
       </c>
@@ -11467,7 +11467,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>19</v>
       </c>
@@ -11526,7 +11526,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>19</v>
       </c>
@@ -11585,7 +11585,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>19</v>
       </c>
@@ -11644,7 +11644,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>19</v>
       </c>
@@ -11703,7 +11703,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>19</v>
       </c>
@@ -11762,7 +11762,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>19</v>
       </c>
@@ -11821,7 +11821,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>19</v>
       </c>
@@ -11880,7 +11880,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>19</v>
       </c>
@@ -11939,7 +11939,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>19</v>
       </c>
@@ -11998,7 +11998,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>19</v>
       </c>
@@ -12057,7 +12057,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>19</v>
       </c>
@@ -12116,7 +12116,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>19</v>
       </c>
@@ -12175,7 +12175,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>19</v>
       </c>
@@ -12234,7 +12234,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>19</v>
       </c>
@@ -12293,7 +12293,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>19</v>
       </c>
@@ -12352,7 +12352,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>19</v>
       </c>
@@ -12411,7 +12411,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>19</v>
       </c>
@@ -12470,7 +12470,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>19</v>
       </c>
@@ -12529,7 +12529,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>19</v>
       </c>
@@ -12588,7 +12588,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>19</v>
       </c>
@@ -12647,7 +12647,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>19</v>
       </c>
@@ -12706,7 +12706,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>19</v>
       </c>
@@ -12765,7 +12765,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>19</v>
       </c>
@@ -12824,7 +12824,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>19</v>
       </c>
@@ -12883,7 +12883,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>19</v>
       </c>
@@ -12942,7 +12942,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>19</v>
       </c>
@@ -13001,7 +13001,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>19</v>
       </c>
@@ -13060,7 +13060,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>19</v>
       </c>
@@ -13119,7 +13119,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>19</v>
       </c>
@@ -13178,7 +13178,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>19</v>
       </c>
@@ -13237,7 +13237,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>19</v>
       </c>
@@ -13296,7 +13296,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>19</v>
       </c>
@@ -13355,7 +13355,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>19</v>
       </c>
@@ -13414,7 +13414,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>19</v>
       </c>
@@ -13473,7 +13473,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>19</v>
       </c>
@@ -13532,7 +13532,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>19</v>
       </c>
@@ -13591,7 +13591,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>19</v>
       </c>
@@ -13650,7 +13650,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>19</v>
       </c>
@@ -13709,7 +13709,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>19</v>
       </c>
@@ -13768,7 +13768,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>19</v>
       </c>
@@ -13827,7 +13827,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>19</v>
       </c>
@@ -13886,7 +13886,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>19</v>
       </c>
@@ -13945,7 +13945,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>19</v>
       </c>
@@ -14004,7 +14004,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>19</v>
       </c>
@@ -14063,7 +14063,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>19</v>
       </c>
@@ -14122,7 +14122,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>19</v>
       </c>
@@ -14181,7 +14181,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>19</v>
       </c>
@@ -14240,7 +14240,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>19</v>
       </c>
@@ -14299,7 +14299,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>19</v>
       </c>
@@ -14358,7 +14358,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>19</v>
       </c>
@@ -14417,7 +14417,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>19</v>
       </c>
@@ -14476,7 +14476,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="202" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>19</v>
       </c>
@@ -14535,7 +14535,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="203" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>19</v>
       </c>
@@ -14594,7 +14594,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="204" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>19</v>
       </c>
@@ -14653,7 +14653,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="205" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>19</v>
       </c>
@@ -14712,7 +14712,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="206" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>19</v>
       </c>
@@ -14771,7 +14771,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>19</v>
       </c>
@@ -14830,7 +14830,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="208" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>19</v>
       </c>
@@ -14889,7 +14889,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>19</v>
       </c>
@@ -14948,7 +14948,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>19</v>
       </c>
@@ -15007,7 +15007,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="211" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>19</v>
       </c>
@@ -15066,7 +15066,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="212" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>19</v>
       </c>
@@ -15125,7 +15125,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>19</v>
       </c>
@@ -15184,7 +15184,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="214" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>19</v>
       </c>
@@ -15243,7 +15243,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>19</v>
       </c>
@@ -15302,7 +15302,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>19</v>
       </c>
@@ -15361,7 +15361,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="217" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>19</v>
       </c>
@@ -15420,7 +15420,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="218" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>19</v>
       </c>
@@ -15479,7 +15479,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="219" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>19</v>
       </c>
@@ -15538,7 +15538,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>19</v>
       </c>
@@ -15597,7 +15597,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="221" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>19</v>
       </c>
@@ -15656,7 +15656,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="222" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>19</v>
       </c>
@@ -15715,7 +15715,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>19</v>
       </c>
@@ -15774,7 +15774,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="224" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>19</v>
       </c>
@@ -15833,7 +15833,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="225" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>19</v>
       </c>
@@ -15892,7 +15892,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="226" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>19</v>
       </c>
@@ -15951,7 +15951,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>19</v>
       </c>
@@ -16010,7 +16010,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="228" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>19</v>
       </c>
@@ -16069,7 +16069,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="229" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>19</v>
       </c>
@@ -16128,7 +16128,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="230" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>19</v>
       </c>
@@ -16187,7 +16187,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>19</v>
       </c>
@@ -16246,7 +16246,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="232" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>19</v>
       </c>
@@ -16305,7 +16305,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="233" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>19</v>
       </c>
@@ -16364,7 +16364,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="234" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>19</v>
       </c>
@@ -16423,7 +16423,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="235" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>19</v>
       </c>
@@ -16482,7 +16482,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="236" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>19</v>
       </c>
@@ -16541,7 +16541,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="237" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>19</v>
       </c>
@@ -16600,7 +16600,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="238" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>19</v>
       </c>
@@ -16659,7 +16659,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="239" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>19</v>
       </c>
@@ -16718,7 +16718,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="240" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>19</v>
       </c>
@@ -16777,7 +16777,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="241" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>19</v>
       </c>
@@ -16836,7 +16836,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="242" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>19</v>
       </c>
@@ -16895,7 +16895,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="243" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>19</v>
       </c>
@@ -16954,7 +16954,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="244" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>19</v>
       </c>
@@ -17013,7 +17013,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="245" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>19</v>
       </c>
@@ -17072,7 +17072,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="246" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>19</v>
       </c>
@@ -17131,7 +17131,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="247" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>19</v>
       </c>
@@ -17190,7 +17190,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="248" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>19</v>
       </c>
@@ -17249,7 +17249,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="249" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>19</v>
       </c>
@@ -17308,7 +17308,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="250" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>19</v>
       </c>
@@ -17367,7 +17367,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="251" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>19</v>
       </c>
@@ -17426,7 +17426,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="252" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>19</v>
       </c>
@@ -17485,7 +17485,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="253" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>19</v>
       </c>
@@ -17544,7 +17544,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="254" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>19</v>
       </c>
@@ -17603,7 +17603,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="255" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>19</v>
       </c>
@@ -17662,7 +17662,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="256" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>19</v>
       </c>
@@ -17721,7 +17721,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="257" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>19</v>
       </c>
@@ -17780,7 +17780,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="258" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>19</v>
       </c>
@@ -17839,7 +17839,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="259" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>19</v>
       </c>
@@ -17898,7 +17898,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="260" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>19</v>
       </c>
@@ -17957,7 +17957,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="261" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>19</v>
       </c>
@@ -18016,7 +18016,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="262" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>19</v>
       </c>
@@ -18075,7 +18075,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="263" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>19</v>
       </c>
@@ -18134,7 +18134,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="264" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>19</v>
       </c>
@@ -18193,7 +18193,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="265" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>19</v>
       </c>
@@ -18252,7 +18252,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="266" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>19</v>
       </c>
@@ -18311,7 +18311,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="267" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>19</v>
       </c>
@@ -18370,7 +18370,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="268" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>19</v>
       </c>
@@ -18429,7 +18429,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="269" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>19</v>
       </c>
@@ -18488,7 +18488,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="270" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>19</v>
       </c>
@@ -18547,7 +18547,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="271" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>19</v>
       </c>
@@ -18606,7 +18606,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="272" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>19</v>
       </c>
@@ -18665,7 +18665,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="273" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>19</v>
       </c>
@@ -18724,7 +18724,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="274" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>19</v>
       </c>
@@ -18783,7 +18783,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="275" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>19</v>
       </c>
@@ -18842,7 +18842,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="276" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>19</v>
       </c>
@@ -18901,7 +18901,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="277" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>19</v>
       </c>
@@ -18960,7 +18960,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="278" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>19</v>
       </c>
@@ -19019,7 +19019,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="279" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>19</v>
       </c>
@@ -19078,7 +19078,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="280" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>19</v>
       </c>
@@ -19137,7 +19137,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="281" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>19</v>
       </c>
@@ -19196,7 +19196,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="282" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>19</v>
       </c>
@@ -19255,7 +19255,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="283" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>19</v>
       </c>
@@ -19314,7 +19314,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="284" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>19</v>
       </c>
@@ -19373,7 +19373,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="285" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>19</v>
       </c>
@@ -19432,7 +19432,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="286" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>19</v>
       </c>
@@ -19491,7 +19491,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="287" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>19</v>
       </c>
@@ -19550,7 +19550,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="288" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>19</v>
       </c>
@@ -19609,7 +19609,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="289" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>19</v>
       </c>
@@ -19668,7 +19668,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="290" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>19</v>
       </c>
@@ -19727,7 +19727,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="291" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>19</v>
       </c>
@@ -19786,7 +19786,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="292" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>19</v>
       </c>
@@ -19845,7 +19845,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="293" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>19</v>
       </c>
@@ -19904,7 +19904,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="294" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>19</v>
       </c>
@@ -19963,7 +19963,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="295" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>19</v>
       </c>
@@ -20022,7 +20022,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="296" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>19</v>
       </c>
@@ -20081,7 +20081,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="297" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>19</v>
       </c>
@@ -20140,7 +20140,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="298" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>19</v>
       </c>
@@ -20199,7 +20199,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="299" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>19</v>
       </c>
@@ -20258,7 +20258,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="300" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>19</v>
       </c>
@@ -20317,7 +20317,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="301" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>19</v>
       </c>
@@ -20376,7 +20376,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="302" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>19</v>
       </c>
@@ -20435,7 +20435,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="303" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>19</v>
       </c>
@@ -20494,7 +20494,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="304" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>19</v>
       </c>
@@ -20553,7 +20553,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="305" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>19</v>
       </c>
@@ -20612,7 +20612,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="306" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>19</v>
       </c>
@@ -20671,7 +20671,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="307" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>19</v>
       </c>
@@ -20730,7 +20730,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="308" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>19</v>
       </c>
@@ -20789,7 +20789,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="309" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>19</v>
       </c>
@@ -20848,7 +20848,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="310" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>19</v>
       </c>
@@ -20907,7 +20907,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="311" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>19</v>
       </c>
@@ -20966,7 +20966,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="312" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>19</v>
       </c>
@@ -21025,7 +21025,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="313" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>19</v>
       </c>
@@ -21084,7 +21084,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="314" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>19</v>
       </c>
@@ -21143,7 +21143,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="315" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>19</v>
       </c>
@@ -21202,7 +21202,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="316" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>19</v>
       </c>
@@ -21261,7 +21261,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="317" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>19</v>
       </c>
@@ -21320,7 +21320,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="318" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>19</v>
       </c>
@@ -21379,7 +21379,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="319" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>19</v>
       </c>
@@ -21438,7 +21438,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="320" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>19</v>
       </c>
@@ -21497,7 +21497,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="321" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>19</v>
       </c>
@@ -21556,7 +21556,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="322" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>19</v>
       </c>
@@ -21615,7 +21615,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="323" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>19</v>
       </c>
@@ -21674,7 +21674,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="324" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>19</v>
       </c>
@@ -21733,7 +21733,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="325" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>19</v>
       </c>
@@ -21792,7 +21792,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="326" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>19</v>
       </c>
@@ -21851,7 +21851,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="327" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>19</v>
       </c>
@@ -21910,7 +21910,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="328" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>19</v>
       </c>
@@ -21969,7 +21969,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="329" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>19</v>
       </c>
@@ -22028,7 +22028,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="330" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>19</v>
       </c>
@@ -22087,7 +22087,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="331" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>19</v>
       </c>
@@ -22146,7 +22146,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="332" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>19</v>
       </c>
@@ -22205,7 +22205,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="333" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>19</v>
       </c>
@@ -22264,7 +22264,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="334" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>19</v>
       </c>
@@ -22323,7 +22323,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="335" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>19</v>
       </c>
@@ -22382,7 +22382,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="336" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>19</v>
       </c>
@@ -22441,7 +22441,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="337" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>19</v>
       </c>
@@ -22500,7 +22500,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="338" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>19</v>
       </c>
@@ -22559,7 +22559,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="339" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>19</v>
       </c>
@@ -22618,7 +22618,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="340" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>19</v>
       </c>
@@ -22677,7 +22677,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="341" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>19</v>
       </c>
@@ -22736,7 +22736,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="342" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>19</v>
       </c>
@@ -22795,7 +22795,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="343" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>19</v>
       </c>
@@ -22854,7 +22854,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="344" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>19</v>
       </c>
@@ -22913,7 +22913,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="345" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>19</v>
       </c>
@@ -22972,7 +22972,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="346" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>19</v>
       </c>
@@ -23031,7 +23031,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="347" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>19</v>
       </c>
@@ -23090,7 +23090,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="348" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>19</v>
       </c>
@@ -23149,7 +23149,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="349" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>19</v>
       </c>
@@ -23208,7 +23208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="350" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>19</v>
       </c>
@@ -23267,7 +23267,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="351" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>19</v>
       </c>
@@ -23326,7 +23326,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="352" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>19</v>
       </c>
@@ -23385,7 +23385,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="353" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>19</v>
       </c>
@@ -23444,7 +23444,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="354" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>19</v>
       </c>
@@ -23503,7 +23503,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="355" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>19</v>
       </c>
@@ -23562,7 +23562,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="356" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>19</v>
       </c>
@@ -23621,7 +23621,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="357" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>19</v>
       </c>
@@ -23680,7 +23680,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="358" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>19</v>
       </c>
@@ -23739,7 +23739,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="359" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>19</v>
       </c>
@@ -23798,7 +23798,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="360" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>19</v>
       </c>
@@ -23857,7 +23857,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="361" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>19</v>
       </c>
@@ -23916,7 +23916,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="362" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>19</v>
       </c>
@@ -23975,7 +23975,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="363" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>19</v>
       </c>
@@ -24034,7 +24034,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="364" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>19</v>
       </c>
@@ -24093,7 +24093,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="365" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>19</v>
       </c>
@@ -24152,7 +24152,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="366" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>19</v>
       </c>
@@ -24211,7 +24211,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="367" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>19</v>
       </c>
@@ -24270,7 +24270,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="368" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>19</v>
       </c>
@@ -24329,7 +24329,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="369" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>19</v>
       </c>
@@ -24388,7 +24388,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="370" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>19</v>
       </c>
@@ -24447,7 +24447,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="371" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>19</v>
       </c>
@@ -24506,7 +24506,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="372" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>19</v>
       </c>
@@ -24565,7 +24565,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="373" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>19</v>
       </c>
@@ -24624,7 +24624,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="374" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>19</v>
       </c>
@@ -24683,7 +24683,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="375" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>19</v>
       </c>
@@ -24742,7 +24742,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="376" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>19</v>
       </c>
@@ -24801,7 +24801,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="377" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>19</v>
       </c>
@@ -24860,7 +24860,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="378" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>19</v>
       </c>
@@ -24919,7 +24919,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="379" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>19</v>
       </c>
@@ -24978,7 +24978,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="380" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>19</v>
       </c>
@@ -25037,7 +25037,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="381" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>19</v>
       </c>
@@ -25096,7 +25096,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="382" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>19</v>
       </c>
@@ -25155,7 +25155,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="383" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>19</v>
       </c>
@@ -25214,7 +25214,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="384" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>19</v>
       </c>
@@ -25273,7 +25273,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="385" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>19</v>
       </c>
@@ -25332,7 +25332,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="386" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>19</v>
       </c>
@@ -25391,7 +25391,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="387" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>19</v>
       </c>
@@ -25450,7 +25450,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="388" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>19</v>
       </c>
@@ -25509,7 +25509,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="389" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>19</v>
       </c>
@@ -25568,7 +25568,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="390" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>19</v>
       </c>
@@ -25627,7 +25627,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="391" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>19</v>
       </c>
@@ -25686,7 +25686,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="392" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>19</v>
       </c>
@@ -25745,7 +25745,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="393" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>19</v>
       </c>
@@ -25804,7 +25804,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="394" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>19</v>
       </c>
@@ -25863,7 +25863,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="395" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>19</v>
       </c>
@@ -25922,7 +25922,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="396" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>19</v>
       </c>
@@ -25981,7 +25981,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="397" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>19</v>
       </c>
@@ -26040,7 +26040,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="398" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>19</v>
       </c>
@@ -26099,7 +26099,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="399" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>19</v>
       </c>
@@ -26158,7 +26158,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="400" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>19</v>
       </c>
@@ -26217,7 +26217,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="401" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>19</v>
       </c>
@@ -26276,7 +26276,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="402" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>19</v>
       </c>
@@ -26335,7 +26335,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="403" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>19</v>
       </c>
@@ -26394,7 +26394,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="404" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>19</v>
       </c>
@@ -26453,7 +26453,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="405" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>19</v>
       </c>
@@ -26512,7 +26512,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="406" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>19</v>
       </c>
@@ -26571,7 +26571,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="407" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>19</v>
       </c>
@@ -26630,7 +26630,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="408" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>19</v>
       </c>
@@ -26689,7 +26689,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="409" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>19</v>
       </c>
@@ -26748,7 +26748,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="410" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>19</v>
       </c>
@@ -26807,7 +26807,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="411" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>19</v>
       </c>
@@ -26866,7 +26866,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="412" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>19</v>
       </c>
@@ -26925,7 +26925,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="413" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>19</v>
       </c>
@@ -26984,7 +26984,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="414" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>19</v>
       </c>
@@ -27043,7 +27043,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="415" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>19</v>
       </c>
@@ -27102,7 +27102,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="416" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>19</v>
       </c>
@@ -27161,7 +27161,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="417" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>19</v>
       </c>
@@ -27220,7 +27220,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="418" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>19</v>
       </c>
@@ -27279,7 +27279,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="419" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>19</v>
       </c>
@@ -27338,7 +27338,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="420" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>19</v>
       </c>
@@ -27397,7 +27397,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="421" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>19</v>
       </c>
@@ -27456,7 +27456,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="422" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>19</v>
       </c>
@@ -27515,7 +27515,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="423" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>19</v>
       </c>
@@ -27574,7 +27574,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="424" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>19</v>
       </c>
@@ -27633,7 +27633,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="425" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>19</v>
       </c>
@@ -27692,7 +27692,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="426" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>19</v>
       </c>
@@ -27751,7 +27751,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="427" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>19</v>
       </c>
@@ -27810,7 +27810,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="428" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>19</v>
       </c>
@@ -27869,7 +27869,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="429" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>19</v>
       </c>
@@ -27928,7 +27928,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="430" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>19</v>
       </c>
@@ -27987,7 +27987,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="431" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>19</v>
       </c>
@@ -28046,7 +28046,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="432" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>19</v>
       </c>
@@ -28105,7 +28105,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="433" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>19</v>
       </c>
@@ -28164,7 +28164,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="434" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>19</v>
       </c>
@@ -28223,7 +28223,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="435" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>19</v>
       </c>
@@ -28282,7 +28282,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="436" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>19</v>
       </c>
@@ -28341,7 +28341,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="437" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>19</v>
       </c>
@@ -28400,7 +28400,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="438" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>19</v>
       </c>
@@ -28459,7 +28459,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="439" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>19</v>
       </c>
@@ -28518,7 +28518,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="440" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>19</v>
       </c>
@@ -28577,7 +28577,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="441" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>19</v>
       </c>
@@ -28636,7 +28636,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="442" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>19</v>
       </c>
@@ -28695,7 +28695,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="443" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>19</v>
       </c>
@@ -28754,7 +28754,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="444" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>19</v>
       </c>
@@ -28813,7 +28813,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="445" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>19</v>
       </c>
@@ -28872,7 +28872,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="446" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>19</v>
       </c>
@@ -28931,7 +28931,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="447" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>19</v>
       </c>
@@ -28990,7 +28990,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="448" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>19</v>
       </c>
@@ -29049,7 +29049,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="449" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>19</v>
       </c>
@@ -29108,7 +29108,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="450" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>19</v>
       </c>
@@ -29167,7 +29167,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="451" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>19</v>
       </c>
@@ -29226,7 +29226,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="452" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>19</v>
       </c>
@@ -29285,7 +29285,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="453" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>19</v>
       </c>
@@ -29344,7 +29344,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="454" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>19</v>
       </c>
@@ -29403,7 +29403,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="455" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>19</v>
       </c>
@@ -29462,7 +29462,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="456" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>19</v>
       </c>
@@ -29521,7 +29521,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="457" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>19</v>
       </c>
@@ -29580,7 +29580,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="458" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>19</v>
       </c>
@@ -29639,7 +29639,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="459" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>19</v>
       </c>
@@ -29698,7 +29698,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="460" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>19</v>
       </c>
@@ -29757,7 +29757,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="461" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>19</v>
       </c>
@@ -29816,7 +29816,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="462" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>19</v>
       </c>
@@ -29875,7 +29875,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="463" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>19</v>
       </c>
@@ -29934,7 +29934,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="464" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>19</v>
       </c>
@@ -29993,7 +29993,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="465" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>19</v>
       </c>
@@ -30052,7 +30052,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="466" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>19</v>
       </c>
@@ -30111,7 +30111,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="467" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>19</v>
       </c>
@@ -30170,7 +30170,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="468" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>19</v>
       </c>
@@ -30229,7 +30229,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="469" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>19</v>
       </c>
@@ -30288,7 +30288,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="470" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>19</v>
       </c>
@@ -30347,7 +30347,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="471" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>19</v>
       </c>
@@ -30406,7 +30406,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="472" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>19</v>
       </c>
@@ -30465,7 +30465,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="473" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>19</v>
       </c>
@@ -30524,7 +30524,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="474" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>19</v>
       </c>
@@ -30583,7 +30583,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="475" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>19</v>
       </c>
@@ -30642,7 +30642,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="476" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>19</v>
       </c>
@@ -30701,7 +30701,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="477" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>19</v>
       </c>
@@ -30760,7 +30760,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="478" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>19</v>
       </c>
@@ -30819,7 +30819,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="479" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>19</v>
       </c>
@@ -30878,7 +30878,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="480" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>19</v>
       </c>
@@ -30937,7 +30937,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="481" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>19</v>
       </c>
@@ -30996,7 +30996,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="482" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>19</v>
       </c>
@@ -31055,7 +31055,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="483" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>19</v>
       </c>
@@ -31114,7 +31114,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="484" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>19</v>
       </c>
@@ -31173,7 +31173,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="485" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>19</v>
       </c>
@@ -31232,7 +31232,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="486" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>19</v>
       </c>
@@ -31291,7 +31291,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="487" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>19</v>
       </c>
@@ -31350,7 +31350,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="488" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>19</v>
       </c>
@@ -31409,7 +31409,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="489" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>19</v>
       </c>
@@ -31468,7 +31468,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="490" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>19</v>
       </c>
@@ -31527,7 +31527,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="491" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>19</v>
       </c>
@@ -31586,7 +31586,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="492" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>19</v>
       </c>
@@ -31645,7 +31645,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="493" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>19</v>
       </c>
@@ -31704,7 +31704,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="494" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>19</v>
       </c>
@@ -31763,7 +31763,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="495" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>19</v>
       </c>
@@ -31822,7 +31822,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="496" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>19</v>
       </c>
@@ -31881,7 +31881,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="497" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>19</v>
       </c>
@@ -31940,7 +31940,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="498" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>19</v>
       </c>
@@ -31999,7 +31999,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="499" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>19</v>
       </c>
@@ -32058,7 +32058,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="500" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>19</v>
       </c>
@@ -32117,7 +32117,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="501" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>19</v>
       </c>
@@ -32176,7 +32176,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="502" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>19</v>
       </c>
@@ -32235,7 +32235,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="503" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>19</v>
       </c>
@@ -32294,7 +32294,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="504" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>19</v>
       </c>
@@ -32353,7 +32353,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="505" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>19</v>
       </c>
@@ -32412,7 +32412,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="506" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>19</v>
       </c>
@@ -32471,7 +32471,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="507" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>19</v>
       </c>
@@ -32530,7 +32530,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="508" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>19</v>
       </c>
@@ -32589,7 +32589,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="509" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>19</v>
       </c>
@@ -32648,7 +32648,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="510" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>19</v>
       </c>
@@ -32707,7 +32707,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="511" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>19</v>
       </c>
@@ -32766,7 +32766,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="512" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>19</v>
       </c>
@@ -32825,7 +32825,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="513" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>19</v>
       </c>
@@ -32884,7 +32884,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="514" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>19</v>
       </c>
@@ -32943,7 +32943,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="515" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>19</v>
       </c>
@@ -33002,7 +33002,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="516" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>19</v>
       </c>
@@ -33061,7 +33061,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="517" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>19</v>
       </c>
@@ -33120,7 +33120,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="518" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>19</v>
       </c>
@@ -33179,7 +33179,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="519" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>19</v>
       </c>
@@ -33238,7 +33238,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="520" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>19</v>
       </c>
@@ -33297,7 +33297,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="521" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>19</v>
       </c>
@@ -33356,7 +33356,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="522" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>19</v>
       </c>
@@ -33415,7 +33415,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="523" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>19</v>
       </c>
@@ -33474,7 +33474,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="524" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>19</v>
       </c>
@@ -33533,7 +33533,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="525" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>19</v>
       </c>
@@ -33592,7 +33592,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="526" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>19</v>
       </c>
@@ -33651,7 +33651,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="527" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>19</v>
       </c>
@@ -33710,7 +33710,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="528" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>19</v>
       </c>
@@ -33769,7 +33769,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="529" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>19</v>
       </c>
@@ -33828,7 +33828,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="530" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>19</v>
       </c>
@@ -33887,7 +33887,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="531" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>19</v>
       </c>
@@ -33946,7 +33946,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="532" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>19</v>
       </c>
@@ -34005,7 +34005,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="533" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>19</v>
       </c>
@@ -34064,7 +34064,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="534" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>19</v>
       </c>
@@ -34123,7 +34123,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="535" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>19</v>
       </c>
@@ -34182,7 +34182,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="536" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>19</v>
       </c>
@@ -34241,7 +34241,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="537" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>19</v>
       </c>
@@ -34300,7 +34300,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="538" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>19</v>
       </c>
@@ -34359,7 +34359,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="539" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>19</v>
       </c>
@@ -34418,7 +34418,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="540" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>19</v>
       </c>
@@ -34477,7 +34477,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="541" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>19</v>
       </c>
@@ -34536,7 +34536,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="542" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>19</v>
       </c>
@@ -34595,7 +34595,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="543" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>19</v>
       </c>
@@ -34654,7 +34654,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="544" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>19</v>
       </c>
@@ -34725,16 +34725,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E71"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="22.875" customWidth="1"/>
+    <col min="2" max="2" width="12.875" customWidth="1"/>
+    <col min="3" max="3" width="16.875" customWidth="1"/>
+    <col min="4" max="4" width="12.875" customWidth="1"/>
+    <col min="5" max="5" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -34751,7 +34751,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>672</v>
       </c>
@@ -34768,7 +34768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>673</v>
       </c>
@@ -34785,7 +34785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>674</v>
       </c>
@@ -34802,7 +34802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>675</v>
       </c>
@@ -34819,7 +34819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>676</v>
       </c>
@@ -34836,7 +34836,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>677</v>
       </c>
@@ -34853,7 +34853,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>678</v>
       </c>
@@ -34870,7 +34870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>679</v>
       </c>
@@ -34887,7 +34887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>680</v>
       </c>
@@ -34904,7 +34904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>681</v>
       </c>
@@ -34921,7 +34921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>682</v>
       </c>
@@ -34938,7 +34938,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>683</v>
       </c>
@@ -34955,7 +34955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>684</v>
       </c>
@@ -34972,7 +34972,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>685</v>
       </c>
@@ -34989,7 +34989,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>686</v>
       </c>
@@ -35006,7 +35006,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>687</v>
       </c>
@@ -35023,7 +35023,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>688</v>
       </c>
@@ -35040,7 +35040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>689</v>
       </c>
@@ -35057,7 +35057,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>690</v>
       </c>
@@ -35074,7 +35074,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>691</v>
       </c>
@@ -35091,7 +35091,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>692</v>
       </c>
@@ -35108,7 +35108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>693</v>
       </c>
@@ -35125,7 +35125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>694</v>
       </c>
@@ -35142,7 +35142,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>695</v>
       </c>
@@ -35159,7 +35159,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>696</v>
       </c>
@@ -35176,7 +35176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>697</v>
       </c>
@@ -35193,7 +35193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>698</v>
       </c>
@@ -35210,7 +35210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>699</v>
       </c>
@@ -35227,7 +35227,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>700</v>
       </c>
@@ -35244,7 +35244,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>701</v>
       </c>
@@ -35261,7 +35261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>702</v>
       </c>
@@ -35278,7 +35278,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>703</v>
       </c>
@@ -35295,7 +35295,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>704</v>
       </c>
@@ -35312,7 +35312,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>705</v>
       </c>
@@ -35329,7 +35329,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>706</v>
       </c>
@@ -35346,7 +35346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>707</v>
       </c>
@@ -35363,7 +35363,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>708</v>
       </c>
@@ -35380,7 +35380,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>709</v>
       </c>
@@ -35397,7 +35397,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>710</v>
       </c>
@@ -35414,7 +35414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>711</v>
       </c>
@@ -35431,7 +35431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>712</v>
       </c>
@@ -35448,7 +35448,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>713</v>
       </c>
@@ -35465,7 +35465,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>714</v>
       </c>
@@ -35482,7 +35482,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>715</v>
       </c>
@@ -35499,7 +35499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>716</v>
       </c>
@@ -35516,7 +35516,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>717</v>
       </c>
@@ -35533,7 +35533,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>718</v>
       </c>
@@ -35550,7 +35550,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>719</v>
       </c>
@@ -35567,7 +35567,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>720</v>
       </c>
@@ -35584,7 +35584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>721</v>
       </c>
@@ -35601,7 +35601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>570</v>
       </c>
@@ -35618,7 +35618,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>576</v>
       </c>
@@ -35635,7 +35635,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>581</v>
       </c>
@@ -35652,7 +35652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>586</v>
       </c>
@@ -35669,7 +35669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>592</v>
       </c>
@@ -35686,7 +35686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>598</v>
       </c>
@@ -35703,7 +35703,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>603</v>
       </c>
@@ -35720,7 +35720,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>608</v>
       </c>
@@ -35737,7 +35737,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>612</v>
       </c>
@@ -35754,7 +35754,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>616</v>
       </c>
@@ -35771,7 +35771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>620</v>
       </c>
@@ -35788,7 +35788,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>625</v>
       </c>
@@ -35805,7 +35805,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>630</v>
       </c>
@@ -35822,7 +35822,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>634</v>
       </c>
@@ -35839,7 +35839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>640</v>
       </c>
@@ -35856,7 +35856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>646</v>
       </c>
@@ -35873,7 +35873,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>651</v>
       </c>
@@ -35890,7 +35890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>655</v>
       </c>
@@ -35907,7 +35907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>659</v>
       </c>
@@ -35924,7 +35924,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>663</v>
       </c>
